--- a/backend/config/methodology2/excel_data/class3_4.xlsx
+++ b/backend/config/methodology2/excel_data/class3_4.xlsx
@@ -199,9 +199,6 @@
     <t>400-11-411-12-495-14-635</t>
   </si>
   <si>
-    <t>635-16-765-20-963</t>
-  </si>
-  <si>
     <t>1130-35-1375-40-1735</t>
   </si>
   <si>
@@ -259,9 +256,6 @@
     <t>E-10</t>
   </si>
   <si>
-    <t>425-12-417-14-549-16-677</t>
-  </si>
-  <si>
     <t>670-20-830-22-1028</t>
   </si>
   <si>
@@ -274,9 +268,6 @@
     <t>E-11</t>
   </si>
   <si>
-    <t>425-12-437-14-549-16-744</t>
-  </si>
-  <si>
     <t>670-20-830-22-1116</t>
   </si>
   <si>
@@ -388,9 +379,6 @@
     <t>E-17</t>
   </si>
   <si>
-    <t>480-14-494-19-708-24-919</t>
-  </si>
-  <si>
     <t>725-26-985-34-1325</t>
   </si>
   <si>
@@ -755,6 +743,18 @@
   </si>
   <si>
     <t>13500-10-27400</t>
+  </si>
+  <si>
+    <t>635-16-763-20-963</t>
+  </si>
+  <si>
+    <t>425-12-437-14-549-16-741</t>
+  </si>
+  <si>
+    <t>480-14-494-19-703-24-919</t>
+  </si>
+  <si>
+    <t>425-12-437-14-549-16-677</t>
   </si>
 </sst>
 </file>
@@ -1014,17 +1014,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1324,8 +1324,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
@@ -1338,17 +1338,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.75">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
@@ -1382,7 +1382,7 @@
         <v>10</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -1408,16 +1408,16 @@
         <v>16</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="31" t="s">
-        <v>211</v>
+      <c r="K3" s="29" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -1443,16 +1443,16 @@
         <v>24</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="31" t="s">
-        <v>212</v>
+      <c r="K4" s="29" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -1478,16 +1478,16 @@
         <v>24</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="31" t="s">
-        <v>212</v>
+      <c r="K5" s="29" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -1513,16 +1513,16 @@
         <v>42</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="31" t="s">
-        <v>213</v>
+      <c r="K6" s="29" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -1548,16 +1548,16 @@
         <v>50</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="32" t="s">
-        <v>214</v>
+      <c r="K7" s="30" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1571,7 +1571,7 @@
         <v>54</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>55</v>
@@ -1583,16 +1583,16 @@
         <v>50</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="32" t="s">
-        <v>214</v>
+      <c r="K8" s="30" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1606,28 +1606,28 @@
         <v>58</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="H9" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="K9" s="32" t="s">
-        <v>215</v>
+        <v>63</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1635,34 +1635,34 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="D10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="G10" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="32" t="s">
-        <v>215</v>
+        <v>63</v>
+      </c>
+      <c r="K10" s="30" t="s">
+        <v>211</v>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
@@ -1673,34 +1673,34 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="H11" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K11" s="32" t="s">
-        <v>216</v>
+        <v>76</v>
+      </c>
+      <c r="K11" s="30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1708,34 +1708,34 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="E12" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="F12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="G12" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>216</v>
+        <v>76</v>
+      </c>
+      <c r="K12" s="30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1743,34 +1743,34 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="F13" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>87</v>
-      </c>
       <c r="G13" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="32" t="s">
-        <v>216</v>
+        <v>76</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1778,34 +1778,34 @@
         <v>12</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="F14" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="G14" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K14" s="32" t="s">
-        <v>216</v>
+        <v>76</v>
+      </c>
+      <c r="K14" s="30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1813,34 +1813,34 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="F15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="G15" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="32" t="s">
-        <v>216</v>
+        <v>76</v>
+      </c>
+      <c r="K15" s="30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1848,34 +1848,34 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="F16" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="G16" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="7" t="s">
+      <c r="H16" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="K16" s="32" t="s">
-        <v>217</v>
+      <c r="K16" s="30" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1883,34 +1883,34 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="F17" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>115</v>
-      </c>
       <c r="G17" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="K17" s="32" t="s">
-        <v>217</v>
+        <v>107</v>
+      </c>
+      <c r="K17" s="30" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1918,34 +1918,34 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="F18" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>120</v>
-      </c>
       <c r="G18" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="K18" s="32" t="s">
-        <v>217</v>
+        <v>107</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1953,34 +1953,34 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="G19" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>217</v>
+        <v>107</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1988,34 +1988,34 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="G20" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" s="11" t="s">
+      <c r="H20" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="K20" s="32" t="s">
-        <v>223</v>
+      <c r="K20" s="30" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1">
@@ -2023,34 +2023,34 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>138</v>
-      </c>
       <c r="G21" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="K21" s="32" t="s">
-        <v>223</v>
+        <v>129</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2058,34 +2058,34 @@
         <v>20</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>143</v>
-      </c>
       <c r="G22" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>223</v>
+        <v>129</v>
+      </c>
+      <c r="K22" s="30" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1">
@@ -2093,34 +2093,34 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="K23" s="32" t="s">
-        <v>223</v>
+        <v>129</v>
+      </c>
+      <c r="K23" s="30" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2128,34 +2128,34 @@
         <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C24" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>150</v>
-      </c>
       <c r="G24" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="K24" s="32" t="s">
-        <v>223</v>
+        <v>129</v>
+      </c>
+      <c r="K24" s="30" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1">
@@ -2163,34 +2163,34 @@
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="K25" s="32" t="s">
-        <v>223</v>
+        <v>129</v>
+      </c>
+      <c r="K25" s="30" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1">
@@ -2198,34 +2198,34 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="G26" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E26" s="11" t="s">
+      <c r="H26" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K26" s="32" t="s">
-        <v>219</v>
+      <c r="K26" s="30" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2235,28 +2235,28 @@
       <c r="B27" s="22"/>
       <c r="C27" s="21"/>
       <c r="D27" s="14" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K27" s="32" t="s">
-        <v>219</v>
+        <v>156</v>
+      </c>
+      <c r="K27" s="30" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2264,34 +2264,34 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C28" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>168</v>
-      </c>
       <c r="G28" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K28" s="32" t="s">
-        <v>219</v>
+        <v>156</v>
+      </c>
+      <c r="K28" s="30" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2299,32 +2299,32 @@
         <v>27</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="14" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K29" s="32" t="s">
-        <v>219</v>
+        <v>156</v>
+      </c>
+      <c r="K29" s="30" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1">
@@ -2332,34 +2332,34 @@
         <v>28</v>
       </c>
       <c r="B30" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="G30" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="D30" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="E30" s="11" t="s">
+      <c r="H30" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="K30" s="32" t="s">
-        <v>220</v>
+      <c r="K30" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2367,34 +2367,34 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="K31" s="32" t="s">
-        <v>220</v>
+        <v>176</v>
+      </c>
+      <c r="K31" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2402,34 +2402,34 @@
         <v>30</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="K32" s="32" t="s">
-        <v>220</v>
+        <v>176</v>
+      </c>
+      <c r="K32" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1">
@@ -2437,34 +2437,34 @@
         <v>31</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="K33" s="32" t="s">
-        <v>220</v>
+        <v>176</v>
+      </c>
+      <c r="K33" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2472,34 +2472,34 @@
         <v>32</v>
       </c>
       <c r="B34" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C34" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>193</v>
-      </c>
       <c r="G34" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="K34" s="32" t="s">
-        <v>220</v>
+        <v>176</v>
+      </c>
+      <c r="K34" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2624,21 +2624,21 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
+      <c r="A1" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2857,21 +2857,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
+      <c r="A1" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2946,21 +2946,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
+      <c r="A1" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3093,23 +3093,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="A1" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>17</v>
@@ -3124,62 +3124,62 @@
         <v>51</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
@@ -4370,93 +4370,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="A1" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>202</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>216</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>

--- a/backend/config/methodology2/excel_data/class3_4.xlsx
+++ b/backend/config/methodology2/excel_data/class3_4.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="248">
   <si>
     <t xml:space="preserve">PAY SCALES OF CLASS 3 &amp; 4  </t>
   </si>
@@ -493,9 +493,6 @@
     <t>32500 - 83800</t>
   </si>
   <si>
-    <t>850-34-1220-40-1620</t>
-  </si>
-  <si>
     <t>1350-60-1650-70-2630</t>
   </si>
   <si>
@@ -755,6 +752,18 @@
   </si>
   <si>
     <t>425-12-437-14-549-16-677</t>
+  </si>
+  <si>
+    <t>E-25</t>
+  </si>
+  <si>
+    <t>800-26-878-34-1014-40-1614</t>
+  </si>
+  <si>
+    <t>850-34-1020-40-1620</t>
+  </si>
+  <si>
+    <t>1300-50-1450-60-1690-70-2600</t>
   </si>
 </sst>
 </file>
@@ -803,7 +812,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -819,6 +828,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -932,7 +953,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1025,6 +1046,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1382,7 +1412,7 @@
         <v>10</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -1408,16 +1438,16 @@
         <v>16</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>18</v>
       </c>
       <c r="K3" s="29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -1443,16 +1473,16 @@
         <v>24</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -1478,16 +1508,16 @@
         <v>24</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>26</v>
       </c>
       <c r="K5" s="29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -1513,16 +1543,16 @@
         <v>42</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -1548,16 +1578,16 @@
         <v>50</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>52</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1571,7 +1601,7 @@
         <v>54</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>55</v>
@@ -1583,16 +1613,16 @@
         <v>50</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>52</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1606,7 +1636,7 @@
         <v>58</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>59</v>
@@ -1618,16 +1648,16 @@
         <v>61</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>63</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1653,16 +1683,16 @@
         <v>61</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>63</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
@@ -1691,16 +1721,16 @@
         <v>74</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>76</v>
       </c>
       <c r="K11" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1711,7 +1741,7 @@
         <v>77</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>78</v>
@@ -1726,16 +1756,16 @@
         <v>74</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>76</v>
       </c>
       <c r="K12" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1746,7 +1776,7 @@
         <v>81</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>82</v>
@@ -1761,16 +1791,16 @@
         <v>74</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>76</v>
       </c>
       <c r="K13" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1796,16 +1826,16 @@
         <v>74</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>76</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1831,16 +1861,16 @@
         <v>74</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>76</v>
       </c>
       <c r="K15" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1866,16 +1896,16 @@
         <v>105</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>107</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1901,16 +1931,16 @@
         <v>105</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>107</v>
       </c>
       <c r="K17" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1920,7 +1950,7 @@
       <c r="B18" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="33" t="s">
         <v>114</v>
       </c>
       <c r="D18" s="14" t="s">
@@ -1936,16 +1966,16 @@
         <v>105</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>107</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1956,7 +1986,7 @@
         <v>118</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>119</v>
@@ -1971,16 +2001,16 @@
         <v>105</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>107</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2006,16 +2036,16 @@
         <v>127</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>129</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1">
@@ -2041,16 +2071,16 @@
         <v>127</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>129</v>
       </c>
       <c r="K21" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2076,16 +2106,16 @@
         <v>127</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>129</v>
       </c>
       <c r="K22" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1">
@@ -2098,11 +2128,11 @@
       <c r="C23" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>138</v>
+      <c r="D23" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>247</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>139</v>
@@ -2111,16 +2141,16 @@
         <v>127</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>129</v>
       </c>
       <c r="K23" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2146,16 +2176,16 @@
         <v>127</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>129</v>
       </c>
       <c r="K24" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1">
@@ -2181,16 +2211,16 @@
         <v>127</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>129</v>
       </c>
       <c r="K25" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1">
@@ -2216,47 +2246,51 @@
         <v>154</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>156</v>
       </c>
       <c r="K26" s="30" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" thickBot="1">
       <c r="A27" s="5">
         <v>25</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="14" t="s">
+      <c r="B27" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="F27" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>159</v>
       </c>
       <c r="G27" s="23" t="s">
         <v>154</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>156</v>
       </c>
       <c r="K27" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2264,34 +2298,34 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="D28" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="E28" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="F28" s="7" t="s">
         <v>163</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>164</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>154</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>156</v>
       </c>
       <c r="K28" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2299,32 +2333,34 @@
         <v>27</v>
       </c>
       <c r="B29" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D29" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="14" t="s">
+      <c r="E29" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="F29" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>154</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>156</v>
       </c>
       <c r="K29" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1">
@@ -2332,34 +2368,34 @@
         <v>28</v>
       </c>
       <c r="B30" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="D30" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="E30" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="F30" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="G30" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="G30" s="9" t="s">
-        <v>174</v>
-      </c>
       <c r="H30" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I30" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>231</v>
-      </c>
       <c r="J30" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K30" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2367,34 +2403,34 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="D31" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E31" s="11" t="s">
+      <c r="F31" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>180</v>
-      </c>
       <c r="G31" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H31" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I31" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="I31" s="9" t="s">
-        <v>231</v>
-      </c>
       <c r="J31" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2402,34 +2438,34 @@
         <v>30</v>
       </c>
       <c r="B32" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="C32" s="25" t="s">
-        <v>182</v>
-      </c>
       <c r="D32" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E32" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>180</v>
-      </c>
       <c r="G32" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H32" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I32" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>231</v>
-      </c>
       <c r="J32" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K32" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1">
@@ -2437,34 +2473,34 @@
         <v>31</v>
       </c>
       <c r="B33" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="20" t="s">
-        <v>184</v>
-      </c>
       <c r="D33" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E33" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>180</v>
-      </c>
       <c r="G33" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H33" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I33" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>231</v>
-      </c>
       <c r="J33" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K33" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2472,34 +2508,34 @@
         <v>32</v>
       </c>
       <c r="B34" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="D34" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="F34" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>189</v>
-      </c>
       <c r="G34" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H34" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="I34" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="I34" s="9" t="s">
-        <v>231</v>
-      </c>
       <c r="J34" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K34" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2947,7 +2983,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -2960,7 +2996,7 @@
         <v>98</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3088,13 +3124,13 @@
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
     <col min="8" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -3109,7 +3145,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>17</v>
@@ -3139,47 +3175,47 @@
         <v>155</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>198</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
@@ -3812,7 +3848,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="9">
-        <v>34600</v>
+        <v>34400</v>
       </c>
       <c r="C22" s="9">
         <v>36200</v>
@@ -3821,7 +3857,7 @@
         <v>36900</v>
       </c>
       <c r="E22" s="9">
-        <v>38100</v>
+        <v>38300</v>
       </c>
       <c r="F22" s="9">
         <v>39900</v>
@@ -3856,7 +3892,7 @@
         <v>38000</v>
       </c>
       <c r="E23" s="9">
-        <v>39100</v>
+        <v>39400</v>
       </c>
       <c r="F23" s="9">
         <v>41100</v>
@@ -4371,7 +4407,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -4386,77 +4422,77 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>215</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B4" s="9">
         <v>1</v>
@@ -4716,7 +4752,7 @@
         <v>38900</v>
       </c>
       <c r="F11" s="9">
-        <v>40300</v>
+        <v>40800</v>
       </c>
       <c r="G11" s="9">
         <v>42400</v>
@@ -5130,7 +5166,7 @@
         <v>52200</v>
       </c>
       <c r="D23" s="9">
-        <v>53800</v>
+        <v>53600</v>
       </c>
       <c r="E23" s="9">
         <v>55500</v>
@@ -5510,7 +5546,7 @@
         <v>74300</v>
       </c>
       <c r="E34" s="9">
-        <v>78800</v>
+        <v>76800</v>
       </c>
       <c r="F34" s="9">
         <v>80500</v>
